--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260713.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,642,027</t>
+          <t>42,584,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>64.81%</t>
+          <t>65.30%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,574,703</t>
+          <t>2,571,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.36%</t>
+          <t>6.18%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,358,000</t>
+          <t>21,329,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,803,267</t>
+          <t>5,795,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,402,286</t>
+          <t>20,374,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>501,000</t>
+          <t>508,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,754,608</t>
+          <t>2,750,608</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,307,901</t>
+          <t>2,303,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,623,285</t>
+          <t>4,617,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>560,222</t>
+          <t>559,222</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,411,296</t>
+          <t>5,403,296</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -880,46 +880,46 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,995,288</t>
+          <t>1,332,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12,839,134</t>
+          <t>1,992,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -941,29 +941,29 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,180,617</t>
+          <t>1,178,617</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>12,821,134</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>5,281,520</t>
+          <t>3,416,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,39 +997,39 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3,421,000</t>
+          <t>5,274,520</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>854,349</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>601,600</t>
+          <t>853,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,22 +1085,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>600,600</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>137,921</t>
+          <t>312,672</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>312,672</t>
+          <t>1,899,321</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,105 +1173,105 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,902,321</t>
+          <t>137,921</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>998,822</t>
+          <t>152,499</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>152,499</t>
+          <t>575,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>575,000</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,213,000</t>
+          <t>998,822</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,22 +1283,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>375,000</t>
+          <t>3,208,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>805,897</t>
+          <t>804,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,827,000</t>
+          <t>1,825,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,704,000</t>
+          <t>5,696,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1381,139 +1381,139 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,193,441</t>
+          <t>1,191,441</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>766,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>767,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10,569,121</t>
+          <t>932,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>4,440,578</t>
+          <t>10,554,121</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>933,659</t>
+          <t>580,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>2,585,703</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,469,981</t>
+          <t>3,464,981</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,374,384</t>
+          <t>1,373,384</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,22 +1591,22 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,589,703</t>
+          <t>4,434,578</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,147,249</t>
+          <t>7,138,249</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,44 +1635,44 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>496,000</t>
+          <t>226,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>495,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -1689,51 +1689,51 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,184,107</t>
+          <t>2,181,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>774,000</t>
+          <t>1,180,076</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,182,076</t>
+          <t>773,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1760,24 +1760,24 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,945,956</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>802,000</t>
+          <t>4,938,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,39 +1811,39 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,555,400</t>
+          <t>801,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>388,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>1,553,400</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1909,29 +1909,29 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>319,000</t>
+          <t>998,121</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,000,121</t>
+          <t>318,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,752,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>1,750,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,66 +2053,66 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>678,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
@@ -2141,44 +2141,44 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>677,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>253,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -2207,56 +2207,100 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>572,516,139</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr"/>
+          <t>334,000</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>408,244,975</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr"/>
+          <t>114,000</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>455,514,683</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>M_NTD</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>406,764,847</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
           <t>RDI_NTD</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>-138,303,708</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr"/>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>-37,881,783</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
